--- a/artfynd/A 51868-2023 artfynd.xlsx
+++ b/artfynd/A 51868-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51868-2023 artfynd.xlsx
+++ b/artfynd/A 51868-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56612779</v>
+        <v>56612776</v>
       </c>
       <c r="B2" t="n">
-        <v>5107</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102185</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Aromia moschata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589162.9907046536</v>
+        <v>589325</v>
       </c>
       <c r="R2" t="n">
-        <v>6613972.612238714</v>
+        <v>6614011</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,24 +743,9 @@
           <t>2015-11-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-11-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56612777</v>
+        <v>56612764</v>
       </c>
       <c r="B3" t="n">
-        <v>5107</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,16 +783,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102185</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Aromia moschata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -832,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589310.3493027193</v>
+        <v>589445</v>
       </c>
       <c r="R3" t="n">
-        <v>6614016.070038386</v>
+        <v>6613815</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,24 +840,14 @@
           <t>2015-11-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-11-24</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Gnagspår</t>
+          <t>Hackspår på tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,12 +877,7 @@
         <v>56612755</v>
       </c>
       <c r="B4" t="n">
-        <v>4711</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589294.7306270468</v>
+        <v>589295</v>
       </c>
       <c r="R4" t="n">
-        <v>6613991.428436052</v>
+        <v>6613991</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,19 +942,9 @@
           <t>2015-11-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2015-11-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1026,37 +976,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>56612776</v>
+        <v>56612777</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>102185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Aromia moschata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589324.6550177503</v>
+        <v>589310</v>
       </c>
       <c r="R5" t="n">
-        <v>6614010.850067493</v>
+        <v>6614016</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,19 +1044,14 @@
           <t>2015-11-24</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2015-11-24</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,15 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>56612781</v>
+        <v>56612779</v>
       </c>
       <c r="B6" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>5173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1154,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>102185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Aromia moschata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1178,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589401.3515291603</v>
+        <v>589163</v>
       </c>
       <c r="R6" t="n">
-        <v>6614044.029321296</v>
+        <v>6613973</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,19 +1146,14 @@
           <t>2015-11-24</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2015-11-24</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>56612774</v>
+        <v>56612775</v>
       </c>
       <c r="B7" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>102977</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1290,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589268.035056065</v>
+        <v>589233</v>
       </c>
       <c r="R7" t="n">
-        <v>6614027.699854055</v>
+        <v>6613965</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,19 +1248,9 @@
           <t>2015-11-24</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2015-11-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,15 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>56612756</v>
+        <v>56612753</v>
       </c>
       <c r="B8" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1378,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589284.3657742762</v>
+        <v>589306</v>
       </c>
       <c r="R8" t="n">
-        <v>6614001.293002868</v>
+        <v>6614078</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,19 +1345,9 @@
           <t>2015-11-24</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2015-11-24</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,15 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>56612778</v>
+        <v>56612772</v>
       </c>
       <c r="B9" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589222.5515110514</v>
+        <v>589328</v>
       </c>
       <c r="R9" t="n">
-        <v>6614023.58108503</v>
+        <v>6613917</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,19 +1442,9 @@
           <t>2015-11-24</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2015-11-24</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,37 +1471,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>56612773</v>
+        <v>56612757</v>
       </c>
       <c r="B10" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>103055</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1626,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589417.9948778145</v>
+        <v>589069</v>
       </c>
       <c r="R10" t="n">
-        <v>6614046.955119304</v>
+        <v>6613962</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1659,19 +1539,9 @@
           <t>2015-11-24</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2015-11-24</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,15 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>56612782</v>
+        <v>56612756</v>
       </c>
       <c r="B11" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589231.0841894163</v>
+        <v>589284</v>
       </c>
       <c r="R11" t="n">
-        <v>6614026.818194437</v>
+        <v>6614001</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,19 +1636,9 @@
           <t>2015-11-24</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2015-11-24</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1807,6 +1662,685 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>56612765</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kvastbruket, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>589443</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6613813</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hubbo</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2015-11-24</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2015-11-24</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Hanna Nilsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Hanna Nilsson, Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>56612773</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kvastbruket, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>589418</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6614047</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hubbo</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2015-11-24</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2015-11-24</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Hanna Nilsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Hanna Nilsson, Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>56612774</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kvastbruket, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>589268</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6614028</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hubbo</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2015-11-24</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2015-11-24</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Hanna Nilsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Hanna Nilsson, Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>56612778</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kvastbruket, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>589223</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6614024</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hubbo</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2015-11-24</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2015-11-24</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Hanna Nilsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Hanna Nilsson, Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>56612781</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kvastbruket, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>589401</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6614044</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hubbo</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2015-11-24</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2015-11-24</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Hanna Nilsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Hanna Nilsson, Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>56612782</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kvastbruket, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>589231</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6614027</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hubbo</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2015-11-24</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2015-11-24</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Hanna Nilsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Hanna Nilsson, Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>56612763</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kvastbruket, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>589439</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6613813</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hubbo</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2015-11-24</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2015-11-24</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Hanna Nilsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Hanna Nilsson, Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51868-2023 artfynd.xlsx
+++ b/artfynd/A 51868-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56612776</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56612764</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56612755</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56612777</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56612779</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56612775</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56612753</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1468,6 +1508,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56612772</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1565,6 +1610,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56612757</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1662,6 +1712,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56612756</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1759,6 +1814,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56612765</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1856,6 +1916,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56612773</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1953,6 +2018,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56612774</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2050,6 +2120,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56612778</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2147,6 +2222,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56612781</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2244,6 +2324,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56612782</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2341,8 +2426,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56612763</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>